--- a/artfynd/A 10782-2020 artfynd.xlsx
+++ b/artfynd/A 10782-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10782-2020 artfynd.xlsx
+++ b/artfynd/A 10782-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4863,10 +4863,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>88634582</v>
+        <v>82767985</v>
       </c>
       <c r="B37" t="n">
-        <v>96334</v>
+        <v>98520</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4875,55 +4875,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Rallvaråsen, ca 400 m NO om (knärot), Vstm</t>
+          <t>Rallvarsåsen, Östra Djupkärra, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>554992.5018543133</v>
+        <v>555455.7554253098</v>
       </c>
       <c r="R37" t="n">
-        <v>6666762.500905799</v>
+        <v>6666657.85718768</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4945,14 +4931,9 @@
           <t>Norberg</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>U-Nor-0261</t>
-        </is>
-      </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -4962,7 +4943,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -4981,142 +4962,21 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>barrnaturskog</t>
+          <t>Barrskog, örtstråk i sluttning</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Carl Hanson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>82767985</v>
-      </c>
-      <c r="B38" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Rallvarsåsen, Östra Djupkärra, Vstm</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>555455.7554253098</v>
-      </c>
-      <c r="R38" t="n">
-        <v>6666657.85718768</v>
-      </c>
-      <c r="S38" t="n">
-        <v>25</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Norberg</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Norberg</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Barrskog, örtstråk i sluttning</t>
-        </is>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
           <t>Tommy Pettersson</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
